--- a/Digital Chess Clock/Grading/2 stage/6-examples/Digital-Chess-Clock_Grading_2-stage_2026-03-12_6-examples_HumanGrading_Claude4.5SonnetGeneration.xlsx
+++ b/Digital Chess Clock/Grading/2 stage/6-examples/Digital-Chess-Clock_Grading_2-stage_2026-03-12_6-examples_HumanGrading_Claude4.5SonnetGeneration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marc-antoinenadeau/Desktop/B.Eng Software Engineering /7th Semester/Capstone/Code/Evaluations/Digital Chess Clock/Grading/2 stage/6-examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C41A0D8A-DC05-C244-BD07-38D1D91C6B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214D3913-8ABE-8346-8A0A-923ED58FF3F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chess Clock" sheetId="1" r:id="rId1"/>
@@ -512,7 +512,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -769,11 +769,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -939,14 +948,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1315,7 +1327,9 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="Type"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="Element"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="Rater 1"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Rater 2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Rater 2">
+      <calculatedColumnFormula>'Chess Clock Grader #2'!C2</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Weighted Cohens Kappa-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -17138,17 +17152,17 @@
         <v>82</v>
       </c>
       <c r="E1" s="31"/>
-      <c r="F1" s="67" t="s">
+      <c r="F1" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="L1" s="69" t="s">
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="L1" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="str">
@@ -17418,17 +17432,17 @@
         <v>1</v>
       </c>
       <c r="E8" s="31"/>
-      <c r="F8" s="67" t="s">
+      <c r="F8" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="L8" s="69" t="s">
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="L8" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="M8" s="70"/>
-      <c r="N8" s="70"/>
+      <c r="M8" s="68"/>
+      <c r="N8" s="68"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="str">
@@ -17695,17 +17709,17 @@
         <v>0</v>
       </c>
       <c r="E15" s="31"/>
-      <c r="F15" s="67" t="s">
+      <c r="F15" s="69" t="s">
         <v>101</v>
       </c>
-      <c r="G15" s="68"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="68"/>
-      <c r="L15" s="69" t="s">
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="L15" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="M15" s="70"/>
-      <c r="N15" s="70"/>
+      <c r="M15" s="68"/>
+      <c r="N15" s="68"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="str">
@@ -17972,17 +17986,17 @@
         <v>1</v>
       </c>
       <c r="E22" s="31"/>
-      <c r="F22" s="67" t="s">
+      <c r="F22" s="69" t="s">
         <v>103</v>
       </c>
-      <c r="G22" s="68"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="68"/>
-      <c r="L22" s="69" t="s">
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70"/>
+      <c r="L22" s="67" t="s">
         <v>104</v>
       </c>
-      <c r="M22" s="70"/>
-      <c r="N22" s="70"/>
+      <c r="M22" s="68"/>
+      <c r="N22" s="68"/>
     </row>
     <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="str">
@@ -18249,17 +18263,17 @@
         <v>1</v>
       </c>
       <c r="E29" s="31"/>
-      <c r="F29" s="67" t="s">
+      <c r="F29" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="G29" s="68"/>
-      <c r="H29" s="68"/>
-      <c r="I29" s="68"/>
-      <c r="L29" s="69" t="s">
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="L29" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="M29" s="70"/>
-      <c r="N29" s="70"/>
+      <c r="M29" s="68"/>
+      <c r="N29" s="68"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="str">
@@ -18526,17 +18540,17 @@
         <v>1</v>
       </c>
       <c r="E36" s="31"/>
-      <c r="F36" s="67" t="s">
+      <c r="F36" s="69" t="s">
         <v>107</v>
       </c>
-      <c r="G36" s="68"/>
-      <c r="H36" s="68"/>
-      <c r="I36" s="68"/>
-      <c r="L36" s="69" t="s">
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="L36" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="M36" s="70"/>
-      <c r="N36" s="70"/>
+      <c r="M36" s="68"/>
+      <c r="N36" s="68"/>
     </row>
     <row r="37" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="str">
@@ -18803,17 +18817,17 @@
         <v>1</v>
       </c>
       <c r="E43" s="31"/>
-      <c r="F43" s="67" t="s">
+      <c r="F43" s="69" t="s">
         <v>109</v>
       </c>
-      <c r="G43" s="68"/>
-      <c r="H43" s="68"/>
-      <c r="I43" s="68"/>
-      <c r="L43" s="69" t="s">
+      <c r="G43" s="70"/>
+      <c r="H43" s="70"/>
+      <c r="I43" s="70"/>
+      <c r="L43" s="67" t="s">
         <v>110</v>
       </c>
-      <c r="M43" s="70"/>
-      <c r="N43" s="70"/>
+      <c r="M43" s="68"/>
+      <c r="N43" s="68"/>
     </row>
     <row r="44" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="4" t="str">
@@ -19080,17 +19094,17 @@
         <v>0</v>
       </c>
       <c r="E50" s="31"/>
-      <c r="F50" s="67" t="s">
+      <c r="F50" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="G50" s="68"/>
-      <c r="H50" s="68"/>
-      <c r="I50" s="68"/>
-      <c r="L50" s="69" t="s">
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="L50" s="67" t="s">
         <v>112</v>
       </c>
-      <c r="M50" s="70"/>
-      <c r="N50" s="70"/>
+      <c r="M50" s="68"/>
+      <c r="N50" s="68"/>
     </row>
     <row r="51" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="4" t="str">
@@ -20342,6 +20356,12 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="L15:N15"/>
     <mergeCell ref="L22:N22"/>
     <mergeCell ref="F50:I50"/>
     <mergeCell ref="L50:N50"/>
@@ -20352,12 +20372,6 @@
     <mergeCell ref="L36:N36"/>
     <mergeCell ref="F43:I43"/>
     <mergeCell ref="L43:N43"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="L15:N15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -20406,18 +20420,18 @@
         <v>82</v>
       </c>
       <c r="E1" s="31"/>
-      <c r="F1" s="67" t="s">
+      <c r="F1" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="L1" s="67" t="s">
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="L1" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
     </row>
     <row r="2" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="str">
@@ -20433,7 +20447,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="4">
-        <f>'Chess Clock Grader #1'!C2</f>
+        <f>'Chess Clock Grader #2'!C2</f>
         <v>1</v>
       </c>
       <c r="E2" s="31"/>
@@ -20503,7 +20517,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <f>'Chess Clock Grader #1'!C3</f>
+        <f>'Chess Clock Grader #2'!C3</f>
         <v>1</v>
       </c>
       <c r="E3" s="31"/>
@@ -20512,7 +20526,7 @@
       </c>
       <c r="G3" s="39">
         <f>COUNTIFS($C$2:$C$90, $F3, $D$2:$D$90, G$2)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H3" s="40">
         <f>COUNTIFS($C$2:$C$46, $F3, $D$2:$D$46, H$2)</f>
@@ -20520,7 +20534,7 @@
       </c>
       <c r="I3" s="41">
         <f>COUNTIFS($C$2:$C$46, $F3, $D$2:$D$46, I$2)+MAX(D47-C47,0)+MAX(D48-C48,0)+MAX(D49-C49,0)+MAX(D50-C50,0)+MAX(D51-C51,0)+MAX(D52-C52,0)+MAX(D53-C53,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="11">
         <f t="shared" ref="J3:J5" si="0">SUM(G3:I3)</f>
@@ -20548,11 +20562,11 @@
       </c>
       <c r="R3" s="39">
         <f t="shared" ref="R3:T3" si="2">($J3/$J$6) * (G$6/$J$6)</f>
-        <v>3.6982248520710061E-2</v>
+        <v>4.0680473372781065E-2</v>
       </c>
       <c r="S3" s="40">
         <f t="shared" si="2"/>
-        <v>3.6982248520710062E-3</v>
+        <v>0</v>
       </c>
       <c r="T3" s="41">
         <f t="shared" si="2"/>
@@ -20564,7 +20578,7 @@
       </c>
       <c r="W3" s="39">
         <f>SUMPRODUCT(G3:I5, M3:O5) /$J$6</f>
-        <v>0</v>
+        <v>4.807692307692308E-2</v>
       </c>
       <c r="X3" s="41" t="s">
         <v>115</v>
@@ -20584,7 +20598,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="4">
-        <f>'Chess Clock Grader #1'!C4</f>
+        <f>'Chess Clock Grader #2'!C4</f>
         <v>1</v>
       </c>
       <c r="E4" s="31"/>
@@ -20593,11 +20607,11 @@
       </c>
       <c r="G4" s="43">
         <f t="shared" ref="G4:I4" si="3">COUNTIFS($C$2:$C$46, $F4, $D$2:$D$46, G$2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="11">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="44">
         <f t="shared" si="3"/>
@@ -20629,11 +20643,11 @@
       </c>
       <c r="R4" s="43">
         <f t="shared" ref="R4:T4" si="5">($J4/$J$6) * (G$6/$J$6)</f>
-        <v>3.6982248520710062E-3</v>
+        <v>4.0680473372781065E-3</v>
       </c>
       <c r="S4" s="11">
         <f t="shared" si="5"/>
-        <v>3.6982248520710064E-4</v>
+        <v>0</v>
       </c>
       <c r="T4" s="44">
         <f t="shared" si="5"/>
@@ -20645,7 +20659,7 @@
       </c>
       <c r="W4" s="43">
         <f>SUMPRODUCT(R3:T5, M3:O5)</f>
-        <v>0.32211538461538458</v>
+        <v>0.32803254437869822</v>
       </c>
       <c r="X4" s="44" t="s">
         <v>117</v>
@@ -20665,7 +20679,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="4">
-        <f>'Chess Clock Grader #1'!C5</f>
+        <f>'Chess Clock Grader #2'!C5</f>
         <v>1</v>
       </c>
       <c r="E5" s="31"/>
@@ -20674,7 +20688,7 @@
       </c>
       <c r="G5" s="45">
         <f>COUNTIFS($C$2:$C$46, $F5, $D$2:$D$46, G$2)+MAX(C47-D47,0)+MAX(C48-D48,0)+MAX(C49-D49,0)+MAX(C50-D50,0)+MAX(C51-D51,0)+MAX(C52-D52,0)+MAX(C53-D53,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="46">
         <f>COUNTIFS($C$2:$C$46, $F5, $D$2:$D$46, H$2)</f>
@@ -20682,7 +20696,7 @@
       </c>
       <c r="I5" s="47">
         <f>COUNTIFS($C$2:$C$46, $F5, $D$2:$D$46, I$2)+ SUM(MIN(C47,D47), MIN(C48,D48), MIN(C49,D49), MIN(C50,D50), MIN(C51,D51), MIN(C52,D52), MIN(C53,D53))</f>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J5" s="11">
         <f t="shared" si="0"/>
@@ -20710,11 +20724,11 @@
       </c>
       <c r="R5" s="45">
         <f t="shared" ref="R5:T5" si="7">($J5/$J$6) * (G$6/$J$6)</f>
-        <v>0.15162721893491124</v>
+        <v>0.16678994082840237</v>
       </c>
       <c r="S5" s="46">
         <f t="shared" si="7"/>
-        <v>1.5162721893491125E-2</v>
+        <v>0</v>
       </c>
       <c r="T5" s="47">
         <f t="shared" si="7"/>
@@ -20726,7 +20740,7 @@
       </c>
       <c r="W5" s="45">
         <f>1-W3/W4</f>
-        <v>1</v>
+        <v>0.85343855693348369</v>
       </c>
       <c r="X5" s="47" t="s">
         <v>118</v>
@@ -20746,7 +20760,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="4">
-        <f>'Chess Clock Grader #1'!C6</f>
+        <f>'Chess Clock Grader #2'!C6</f>
         <v>1</v>
       </c>
       <c r="E6" s="31"/>
@@ -20755,11 +20769,11 @@
       </c>
       <c r="G6" s="11">
         <f t="shared" ref="G6:I6" si="8">SUM(G3:G5)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H6" s="11">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="11">
         <f t="shared" si="8"/>
@@ -20795,7 +20809,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="4">
-        <f>'Chess Clock Grader #1'!C7</f>
+        <f>'Chess Clock Grader #2'!C7</f>
         <v>1</v>
       </c>
       <c r="E7" s="31"/>
@@ -20817,16 +20831,16 @@
         <v>1</v>
       </c>
       <c r="D8" s="4">
-        <f>'Chess Clock Grader #1'!C8</f>
+        <f>'Chess Clock Grader #2'!C8</f>
         <v>1</v>
       </c>
       <c r="E8" s="31"/>
-      <c r="F8" s="67" t="s">
+      <c r="F8" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
     </row>
     <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="str">
@@ -20842,7 +20856,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="4">
-        <f>'Chess Clock Grader #1'!C9</f>
+        <f>'Chess Clock Grader #2'!C9</f>
         <v>1</v>
       </c>
       <c r="E9" s="31"/>
@@ -20912,7 +20926,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="4">
-        <f>'Chess Clock Grader #1'!C10</f>
+        <f>'Chess Clock Grader #2'!C10</f>
         <v>1</v>
       </c>
       <c r="E10" s="31"/>
@@ -20957,11 +20971,11 @@
       </c>
       <c r="R10" s="39">
         <f t="shared" ref="R10:T10" si="12">($J10/$J$13) * (G$13/$J$13)</f>
-        <v>2.0408163265306121E-2</v>
+        <v>3.0612244897959179E-2</v>
       </c>
       <c r="S10" s="40">
         <f t="shared" si="12"/>
-        <v>1.020408163265306E-2</v>
+        <v>0</v>
       </c>
       <c r="T10" s="41">
         <f t="shared" si="12"/>
@@ -20973,7 +20987,7 @@
       </c>
       <c r="W10" s="39">
         <f>SUMPRODUCT(G10:I12, M10:O12) /$J$13</f>
-        <v>0</v>
+        <v>3.5714285714285712E-2</v>
       </c>
       <c r="X10" s="41" t="s">
         <v>115</v>
@@ -20993,7 +21007,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="4">
-        <f>'Chess Clock Grader #1'!C11</f>
+        <f>'Chess Clock Grader #2'!C11</f>
         <v>1</v>
       </c>
       <c r="E11" s="31"/>
@@ -21002,11 +21016,11 @@
       </c>
       <c r="G11" s="43">
         <f t="shared" ref="G11:I11" si="13">COUNTIFS($A$2:$A$90,$F$9,$C$2:$C$90,$F11,$D$2:$D$90,G$9)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="11">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="44">
         <f t="shared" si="13"/>
@@ -21038,11 +21052,11 @@
       </c>
       <c r="R11" s="43">
         <f t="shared" ref="R11:T11" si="15">($J11/$J$13) * (G$13/$J$13)</f>
-        <v>1.020408163265306E-2</v>
+        <v>1.530612244897959E-2</v>
       </c>
       <c r="S11" s="11">
         <f t="shared" si="15"/>
-        <v>5.1020408163265302E-3</v>
+        <v>0</v>
       </c>
       <c r="T11" s="44">
         <f t="shared" si="15"/>
@@ -21054,7 +21068,7 @@
       </c>
       <c r="W11" s="43">
         <f>SUMPRODUCT(R10:T12, M10:O12)</f>
-        <v>0.29081632653061223</v>
+        <v>0.31632653061224486</v>
       </c>
       <c r="X11" s="44" t="s">
         <v>117</v>
@@ -21074,7 +21088,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="4">
-        <f>'Chess Clock Grader #1'!C12</f>
+        <f>'Chess Clock Grader #2'!C12</f>
         <v>1</v>
       </c>
       <c r="E12" s="31"/>
@@ -21119,11 +21133,11 @@
       </c>
       <c r="R12" s="45">
         <f t="shared" ref="R12:T12" si="17">($J12/$J$13) * (G$13/$J$13)</f>
-        <v>0.11224489795918366</v>
+        <v>0.1683673469387755</v>
       </c>
       <c r="S12" s="46">
         <f t="shared" si="17"/>
-        <v>5.612244897959183E-2</v>
+        <v>0</v>
       </c>
       <c r="T12" s="47">
         <f t="shared" si="17"/>
@@ -21135,7 +21149,7 @@
       </c>
       <c r="W12" s="45">
         <f>1-W10/W11</f>
-        <v>1</v>
+        <v>0.88709677419354838</v>
       </c>
       <c r="X12" s="47" t="s">
         <v>118</v>
@@ -21155,7 +21169,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="4">
-        <f>'Chess Clock Grader #1'!C13</f>
+        <f>'Chess Clock Grader #2'!C13</f>
         <v>1</v>
       </c>
       <c r="E13" s="31"/>
@@ -21164,11 +21178,11 @@
       </c>
       <c r="G13" s="11">
         <f t="shared" ref="G13:I13" si="18">SUM(G10:G12)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H13" s="11">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="11">
         <f t="shared" si="18"/>
@@ -21193,7 +21207,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="4">
-        <f>'Chess Clock Grader #1'!C14</f>
+        <f>'Chess Clock Grader #2'!C14</f>
         <v>1</v>
       </c>
       <c r="E14" s="31"/>
@@ -21212,16 +21226,16 @@
         <v>0</v>
       </c>
       <c r="D15" s="4">
-        <f>'Chess Clock Grader #1'!C15</f>
+        <f>'Chess Clock Grader #2'!C15</f>
         <v>0</v>
       </c>
       <c r="E15" s="31"/>
-      <c r="F15" s="67" t="s">
+      <c r="F15" s="69" t="s">
         <v>101</v>
       </c>
-      <c r="G15" s="68"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="68"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
     </row>
     <row r="16" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="str">
@@ -21237,8 +21251,8 @@
         <v>1</v>
       </c>
       <c r="D16" s="4">
-        <f>'Chess Clock Grader #1'!C16</f>
-        <v>1</v>
+        <f>'Chess Clock Grader #2'!C16</f>
+        <v>0</v>
       </c>
       <c r="E16" s="31"/>
       <c r="F16" s="11" t="s">
@@ -21307,7 +21321,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="4">
-        <f>'Chess Clock Grader #1'!C17</f>
+        <f>'Chess Clock Grader #2'!C17</f>
         <v>1</v>
       </c>
       <c r="E17" s="31"/>
@@ -21316,7 +21330,7 @@
       </c>
       <c r="G17" s="39">
         <f t="shared" ref="G17:H17" si="19">COUNTIFS($A$2:$A$90,$F$16,$C$2:$C$90,$F17,$D$2:$D$90,G$16)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17" s="40">
         <f t="shared" si="19"/>
@@ -21324,7 +21338,7 @@
       </c>
       <c r="I17" s="41">
         <f>COUNTIFS($A$2:$A$46,$F$16,$C$2:$C$46,$F17,$D$2:$D$46,I$16) + MAX(D48-C48,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="11">
         <f t="shared" ref="J17:J19" si="20">SUM(G17:I17)</f>
@@ -21352,7 +21366,7 @@
       </c>
       <c r="R17" s="39">
         <f t="shared" ref="R17:T17" si="22">($J17/$J$20) * (G$20/$J$20)</f>
-        <v>4.0000000000000008E-2</v>
+        <v>2.6666666666666668E-2</v>
       </c>
       <c r="S17" s="40">
         <f t="shared" si="22"/>
@@ -21360,7 +21374,7 @@
       </c>
       <c r="T17" s="41">
         <f t="shared" si="22"/>
-        <v>0.16000000000000003</v>
+        <v>0.17333333333333334</v>
       </c>
       <c r="U17" s="11"/>
       <c r="V17" s="42" t="s">
@@ -21368,7 +21382,7 @@
       </c>
       <c r="W17" s="39">
         <f>SUMPRODUCT(G17:I19, M17:O19) /$J$20</f>
-        <v>0</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="X17" s="41" t="s">
         <v>115</v>
@@ -21388,7 +21402,7 @@
         <v>1</v>
       </c>
       <c r="D18" s="4">
-        <f>'Chess Clock Grader #1'!C18</f>
+        <f>'Chess Clock Grader #2'!C18</f>
         <v>1</v>
       </c>
       <c r="E18" s="31"/>
@@ -21449,7 +21463,7 @@
       </c>
       <c r="W18" s="43">
         <f>SUMPRODUCT(R17:T19, M17:O19)</f>
-        <v>0.32000000000000006</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="X18" s="44" t="s">
         <v>117</v>
@@ -21469,7 +21483,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="4">
-        <f>'Chess Clock Grader #1'!C19</f>
+        <f>'Chess Clock Grader #2'!C19</f>
         <v>1</v>
       </c>
       <c r="E19" s="31"/>
@@ -21514,7 +21528,7 @@
       </c>
       <c r="R19" s="45">
         <f t="shared" ref="R19:T19" si="27">($J19/$J$20) * (G$20/$J$20)</f>
-        <v>0.16000000000000003</v>
+        <v>0.10666666666666667</v>
       </c>
       <c r="S19" s="46">
         <f t="shared" si="27"/>
@@ -21522,7 +21536,7 @@
       </c>
       <c r="T19" s="47">
         <f t="shared" si="27"/>
-        <v>0.64000000000000012</v>
+        <v>0.69333333333333336</v>
       </c>
       <c r="U19" s="11"/>
       <c r="V19" s="42" t="s">
@@ -21530,7 +21544,7 @@
       </c>
       <c r="W19" s="45">
         <f>1-W17/W18</f>
-        <v>1</v>
+        <v>0.76190476190476186</v>
       </c>
       <c r="X19" s="47" t="s">
         <v>118</v>
@@ -21550,7 +21564,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="4">
-        <f>'Chess Clock Grader #1'!C20</f>
+        <f>'Chess Clock Grader #2'!C20</f>
         <v>1</v>
       </c>
       <c r="E20" s="31"/>
@@ -21559,7 +21573,7 @@
       </c>
       <c r="G20" s="11">
         <f t="shared" ref="G20:I20" si="28">SUM(G17:G19)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="11">
         <f t="shared" si="28"/>
@@ -21567,7 +21581,7 @@
       </c>
       <c r="I20" s="11">
         <f t="shared" si="28"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J20" s="11">
         <f>SUM(G17:I19)</f>
@@ -21588,7 +21602,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="4">
-        <f>'Chess Clock Grader #1'!C21</f>
+        <f>'Chess Clock Grader #2'!C21</f>
         <v>1</v>
       </c>
       <c r="E21" s="31"/>
@@ -21607,16 +21621,16 @@
         <v>1</v>
       </c>
       <c r="D22" s="4">
-        <f>'Chess Clock Grader #1'!C22</f>
+        <f>'Chess Clock Grader #2'!C22</f>
         <v>1</v>
       </c>
       <c r="E22" s="31"/>
-      <c r="F22" s="67" t="s">
+      <c r="F22" s="69" t="s">
         <v>103</v>
       </c>
-      <c r="G22" s="68"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="68"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70"/>
     </row>
     <row r="23" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="str">
@@ -21632,7 +21646,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="4">
-        <f>'Chess Clock Grader #1'!C23</f>
+        <f>'Chess Clock Grader #2'!C23</f>
         <v>0</v>
       </c>
       <c r="E23" s="31"/>
@@ -21702,7 +21716,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="4">
-        <f>'Chess Clock Grader #1'!C24</f>
+        <f>'Chess Clock Grader #2'!C24</f>
         <v>1</v>
       </c>
       <c r="E24" s="31"/>
@@ -21783,7 +21797,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="4">
-        <f>'Chess Clock Grader #1'!C25</f>
+        <f>'Chess Clock Grader #2'!C25</f>
         <v>1</v>
       </c>
       <c r="E25" s="31"/>
@@ -21864,7 +21878,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="4">
-        <f>'Chess Clock Grader #1'!C26</f>
+        <f>'Chess Clock Grader #2'!C26</f>
         <v>1</v>
       </c>
       <c r="E26" s="31"/>
@@ -21945,7 +21959,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="4">
-        <f>'Chess Clock Grader #1'!C27</f>
+        <f>'Chess Clock Grader #2'!C27</f>
         <v>1</v>
       </c>
       <c r="E27" s="31"/>
@@ -21983,7 +21997,7 @@
         <v>1</v>
       </c>
       <c r="D28" s="4">
-        <f>'Chess Clock Grader #1'!C28</f>
+        <f>'Chess Clock Grader #2'!C28</f>
         <v>1</v>
       </c>
       <c r="E28" s="31"/>
@@ -22002,16 +22016,16 @@
         <v>1</v>
       </c>
       <c r="D29" s="4">
-        <f>'Chess Clock Grader #1'!C29</f>
+        <f>'Chess Clock Grader #2'!C29</f>
         <v>1</v>
       </c>
       <c r="E29" s="31"/>
-      <c r="F29" s="67" t="s">
+      <c r="F29" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="G29" s="68"/>
-      <c r="H29" s="68"/>
-      <c r="I29" s="68"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
     </row>
     <row r="30" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="str">
@@ -22027,7 +22041,7 @@
         <v>1</v>
       </c>
       <c r="D30" s="4">
-        <f>'Chess Clock Grader #1'!C30</f>
+        <f>'Chess Clock Grader #2'!C30</f>
         <v>1</v>
       </c>
       <c r="E30" s="31"/>
@@ -22097,7 +22111,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="4">
-        <f>'Chess Clock Grader #1'!C31</f>
+        <f>'Chess Clock Grader #2'!C31</f>
         <v>1</v>
       </c>
       <c r="E31" s="31"/>
@@ -22178,7 +22192,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="4">
-        <f>'Chess Clock Grader #1'!C32</f>
+        <f>'Chess Clock Grader #2'!C32</f>
         <v>1</v>
       </c>
       <c r="E32" s="31"/>
@@ -22259,7 +22273,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="4">
-        <f>'Chess Clock Grader #1'!C33</f>
+        <f>'Chess Clock Grader #2'!C33</f>
         <v>1</v>
       </c>
       <c r="E33" s="31"/>
@@ -22340,7 +22354,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="4">
-        <f>'Chess Clock Grader #1'!C34</f>
+        <f>'Chess Clock Grader #2'!C34</f>
         <v>1</v>
       </c>
       <c r="E34" s="31"/>
@@ -22378,7 +22392,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="4">
-        <f>'Chess Clock Grader #1'!C35</f>
+        <f>'Chess Clock Grader #2'!C35</f>
         <v>1</v>
       </c>
       <c r="E35" s="31"/>
@@ -22397,16 +22411,16 @@
         <v>1</v>
       </c>
       <c r="D36" s="4">
-        <f>'Chess Clock Grader #1'!C36</f>
+        <f>'Chess Clock Grader #2'!C36</f>
         <v>1</v>
       </c>
       <c r="E36" s="31"/>
-      <c r="F36" s="67" t="s">
+      <c r="F36" s="69" t="s">
         <v>107</v>
       </c>
-      <c r="G36" s="68"/>
-      <c r="H36" s="68"/>
-      <c r="I36" s="68"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
     </row>
     <row r="37" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="str">
@@ -22422,7 +22436,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="4">
-        <f>'Chess Clock Grader #1'!C37</f>
+        <f>'Chess Clock Grader #2'!C37</f>
         <v>1</v>
       </c>
       <c r="E37" s="31"/>
@@ -22492,7 +22506,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="4">
-        <f>'Chess Clock Grader #1'!C38</f>
+        <f>'Chess Clock Grader #2'!C38</f>
         <v>1</v>
       </c>
       <c r="E38" s="31"/>
@@ -22573,7 +22587,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="4">
-        <f>'Chess Clock Grader #1'!C39</f>
+        <f>'Chess Clock Grader #2'!C39</f>
         <v>1</v>
       </c>
       <c r="E39" s="31"/>
@@ -22654,8 +22668,8 @@
         <v>0</v>
       </c>
       <c r="D40" s="4">
-        <f>'Chess Clock Grader #1'!C40</f>
-        <v>0</v>
+        <f>'Chess Clock Grader #2'!C40</f>
+        <v>1</v>
       </c>
       <c r="E40" s="31"/>
       <c r="F40" s="38">
@@ -22735,7 +22749,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="4">
-        <f>'Chess Clock Grader #1'!C41</f>
+        <f>'Chess Clock Grader #2'!C41</f>
         <v>1</v>
       </c>
       <c r="E41" s="31"/>
@@ -22773,7 +22787,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="4">
-        <f>'Chess Clock Grader #1'!C42</f>
+        <f>'Chess Clock Grader #2'!C42</f>
         <v>1</v>
       </c>
       <c r="E42" s="31"/>
@@ -22792,16 +22806,16 @@
         <v>1</v>
       </c>
       <c r="D43" s="4">
-        <f>'Chess Clock Grader #1'!C43</f>
+        <f>'Chess Clock Grader #2'!C43</f>
         <v>1</v>
       </c>
       <c r="E43" s="31"/>
-      <c r="F43" s="67" t="s">
+      <c r="F43" s="69" t="s">
         <v>109</v>
       </c>
-      <c r="G43" s="68"/>
-      <c r="H43" s="68"/>
-      <c r="I43" s="68"/>
+      <c r="G43" s="70"/>
+      <c r="H43" s="70"/>
+      <c r="I43" s="70"/>
     </row>
     <row r="44" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="4" t="str">
@@ -22817,7 +22831,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="4">
-        <f>'Chess Clock Grader #1'!C44</f>
+        <f>'Chess Clock Grader #2'!C44</f>
         <v>1</v>
       </c>
       <c r="E44" s="31"/>
@@ -22887,8 +22901,8 @@
         <v>0.5</v>
       </c>
       <c r="D45" s="4">
-        <f>'Chess Clock Grader #1'!C45</f>
-        <v>0.5</v>
+        <f>'Chess Clock Grader #2'!C45</f>
+        <v>0</v>
       </c>
       <c r="E45" s="31"/>
       <c r="F45" s="38">
@@ -22967,8 +22981,8 @@
         <f>'Chess Clock Grader #1'!C46</f>
         <v>1</v>
       </c>
-      <c r="D46" s="4">
-        <f>'Chess Clock Grader #1'!C46</f>
+      <c r="D46" s="71">
+        <f>'Chess Clock Grader #2'!C46</f>
         <v>1</v>
       </c>
       <c r="E46" s="31"/>
@@ -23048,8 +23062,8 @@
         <f>'Chess Clock Grader #1'!C47</f>
         <v>0</v>
       </c>
-      <c r="D47" s="52">
-        <f>'Chess Clock Grader #1'!C47</f>
+      <c r="D47" s="4">
+        <f>'Chess Clock Grader #2'!C47</f>
         <v>0</v>
       </c>
       <c r="E47" s="31"/>
@@ -23130,7 +23144,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="4">
-        <f>'Chess Clock Grader #1'!C48</f>
+        <f>'Chess Clock Grader #2'!C48</f>
         <v>0</v>
       </c>
       <c r="E48" s="31"/>
@@ -23168,7 +23182,7 @@
         <v>0</v>
       </c>
       <c r="D49" s="4">
-        <f>'Chess Clock Grader #1'!C49</f>
+        <f>'Chess Clock Grader #2'!C49</f>
         <v>0</v>
       </c>
       <c r="E49" s="31"/>
@@ -23187,16 +23201,16 @@
         <v>0</v>
       </c>
       <c r="D50" s="4">
-        <f>'Chess Clock Grader #1'!C50</f>
+        <f>'Chess Clock Grader #2'!C50</f>
         <v>0</v>
       </c>
       <c r="E50" s="31"/>
-      <c r="F50" s="67" t="s">
+      <c r="F50" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="G50" s="68"/>
-      <c r="H50" s="68"/>
-      <c r="I50" s="68"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
     </row>
     <row r="51" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="4" t="str">
@@ -23212,7 +23226,7 @@
         <v>0</v>
       </c>
       <c r="D51" s="4">
-        <f>'Chess Clock Grader #1'!C51</f>
+        <f>'Chess Clock Grader #2'!C51</f>
         <v>0</v>
       </c>
       <c r="E51" s="31"/>
@@ -23282,7 +23296,7 @@
         <v>0</v>
       </c>
       <c r="D52" s="4">
-        <f>'Chess Clock Grader #1'!C52</f>
+        <f>'Chess Clock Grader #2'!C52</f>
         <v>0</v>
       </c>
       <c r="E52" s="31"/>
@@ -23327,7 +23341,7 @@
       </c>
       <c r="R52" s="39">
         <f t="shared" ref="R52:T52" si="72">($J52/$J$55) * (G$55/$J$55)</f>
-        <v>0.1111111111111111</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="S52" s="40">
         <f t="shared" si="72"/>
@@ -23335,7 +23349,7 @@
       </c>
       <c r="T52" s="41">
         <f t="shared" si="72"/>
-        <v>0.22222222222222221</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U52" s="11"/>
       <c r="V52" s="42" t="s">
@@ -23343,7 +23357,7 @@
       </c>
       <c r="W52" s="39">
         <f>SUMPRODUCT(G52:I54, M52:O54) /$J$55</f>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="X52" s="41" t="s">
         <v>115</v>
@@ -23363,7 +23377,7 @@
         <v>0</v>
       </c>
       <c r="D53" s="4">
-        <f>'Chess Clock Grader #1'!C53</f>
+        <f>'Chess Clock Grader #2'!C53</f>
         <v>0</v>
       </c>
       <c r="E53" s="31"/>
@@ -23424,7 +23438,7 @@
       </c>
       <c r="W53" s="43">
         <f>SUMPRODUCT(R52:T54, M52:O54)</f>
-        <v>0.44444444444444442</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="X53" s="44" t="s">
         <v>117</v>
@@ -23441,7 +23455,7 @@
       </c>
       <c r="G54" s="45">
         <f>COUNTIFS($A$2:$A$46,$F$51,$C$2:$C$46,$F54,$D$2:$D$46,G$51) + MAX(C52-D52,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" s="46">
         <f>COUNTIFS($A$2:$A$90,$F$51,$C$2:$C$90,$F54,$D$2:$D$90,H$51)</f>
@@ -23449,7 +23463,7 @@
       </c>
       <c r="I54" s="47">
         <f>COUNTIFS($A$2:$A$46,$F$51,$C$2:$C$46,$F54,$D$2:$D$46,I$51)+MIN(C52,D52)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J54" s="11">
         <f t="shared" si="70"/>
@@ -23477,7 +23491,7 @@
       </c>
       <c r="R54" s="45">
         <f t="shared" ref="R54:T54" si="77">($J54/$J$55) * (G$55/$J$55)</f>
-        <v>0.22222222222222221</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="S54" s="46">
         <f t="shared" si="77"/>
@@ -23485,7 +23499,7 @@
       </c>
       <c r="T54" s="47">
         <f t="shared" si="77"/>
-        <v>0.44444444444444442</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="U54" s="11"/>
       <c r="V54" s="42" t="s">
@@ -23493,7 +23507,7 @@
       </c>
       <c r="W54" s="45">
         <f>1-W52/W53</f>
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="X54" s="47" t="s">
         <v>118</v>
@@ -23510,7 +23524,7 @@
       </c>
       <c r="G55" s="11">
         <f t="shared" ref="G55:I55" si="78">SUM(G52:G54)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H55" s="11">
         <f t="shared" si="78"/>
@@ -23518,7 +23532,7 @@
       </c>
       <c r="I55" s="11">
         <f t="shared" si="78"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J55" s="11">
         <f>SUM(G52:I54)</f>
